--- a/tools/importer/reports/import-demo.report.xlsx
+++ b/tools/importer/reports/import-demo.report.xlsx
@@ -67,7 +67,7 @@
     <t>demo</t>
   </si>
   <si>
-    <t>2026-09-25T14:41:13.151Z</t>
+    <t>2026-10-15T11:40:05.409Z</t>
   </si>
   <si>
     <t>Basic HTML Test Page</t>
